--- a/output/pdf_financials_xlsx/TGOL.xlsx
+++ b/output/pdf_financials_xlsx/TGOL.xlsx
@@ -4821,34 +4821,34 @@
         <v>1.152205</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.609834</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.631484</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.700032</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>0.694074</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>0.772995</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.038365</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>1.484527</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>1.843248</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>1.908968</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.380947</v>
       </c>
     </row>
     <row r="93">
@@ -6026,31 +6026,31 @@
         <v>-0.017926</v>
       </c>
       <c r="E118" s="3" t="n">
-        <v>0.721333</v>
+        <v>0.306766</v>
       </c>
       <c r="F118" s="3" t="n">
-        <v>0.146937</v>
+        <v>-0.166092</v>
       </c>
       <c r="G118" s="3" t="n">
-        <v>0.877221</v>
+        <v>0.47563</v>
       </c>
       <c r="H118" s="3" t="n">
-        <v>0.8585930000000001</v>
+        <v>0.340457</v>
       </c>
       <c r="I118" s="3" t="n">
-        <v>0.600641</v>
+        <v>-1.071363</v>
       </c>
       <c r="J118" s="3" t="n">
-        <v>0.285236</v>
+        <v>-2.333183</v>
       </c>
       <c r="K118" s="3" t="n">
-        <v>0.059</v>
+        <v>-2.022023</v>
       </c>
       <c r="L118" s="3" t="n">
-        <v>0.445094</v>
+        <v>0.025855</v>
       </c>
       <c r="M118" s="3" t="n">
-        <v>0.062933</v>
+        <v>-0.905911</v>
       </c>
     </row>
     <row r="119">
@@ -7866,7 +7866,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E15" t="inlineStr">
         <is>
           <t>-</t>
@@ -11780,7 +11784,11 @@
           <t>Exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -14598,7 +14606,11 @@
           <t>Grants received for exploration and evaluation expenditures</t>
         </is>
       </c>
-      <c r="D109" t="inlineStr"/>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E109" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/TGOL.xlsx
+++ b/output/pdf_financials_xlsx/TGOL.xlsx
@@ -921,34 +921,34 @@
         </is>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>3.4e-05</v>
       </c>
       <c r="F12" s="3" t="n">
         <v>0</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>0.000267</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>7.6e-05</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>0.001144</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>0.002439</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>0.017756</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>0.044218</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>0.020104</v>
       </c>
     </row>
     <row r="13">
@@ -1686,34 +1686,34 @@
         </is>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.757602</v>
+        <v>-0.757636</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.14941</v>
+        <v>-0.149444</v>
       </c>
       <c r="F27" s="3" t="n">
         <v>-0.14941</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.930355</v>
+        <v>-0.9306219999999999</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-0.393858</v>
+        <v>-0.393934</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.651733</v>
+        <v>0.650589</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-1.066909</v>
+        <v>-1.069348</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-0.621649</v>
+        <v>-0.639405</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-0.714592</v>
+        <v>-0.75881</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-1.152395</v>
+        <v>-1.172499</v>
       </c>
     </row>
     <row r="28">
@@ -1780,34 +1780,34 @@
         </is>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.757602</v>
+        <v>-0.757636</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.14941</v>
+        <v>-0.149444</v>
       </c>
       <c r="F29" s="3" t="n">
         <v>-0.14941</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.930355</v>
+        <v>-0.9306219999999999</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-0.393858</v>
+        <v>-0.393934</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.653002</v>
+        <v>0.651858</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.063057</v>
+        <v>-1.065496</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.6115660000000001</v>
+        <v>-0.629322</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.7015169999999999</v>
+        <v>-0.745735</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-1.137469</v>
+        <v>-1.157573</v>
       </c>
     </row>
     <row r="30">
@@ -2004,45 +2004,41 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0.084971</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0.01721</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.070811</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.205829</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.091948</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.062272</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.359683</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>2.893196</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>1.125958</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>1.505119</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.501736</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>1.077924</v>
       </c>
     </row>
     <row r="35">
@@ -2095,40 +2091,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0.037211</v>
+        <v>0.122182</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0.02825</v>
+        <v>0.04546</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0.025375</v>
+        <v>0.09618599999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0.0075</v>
+        <v>0.213329</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0.046401</v>
+        <v>0.138349</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0.019885</v>
+        <v>0.08215699999999999</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0.154713</v>
+        <v>0.514396</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0.818424</v>
+        <v>3.71162</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.54894</v>
+        <v>1.674898</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.324809</v>
+        <v>1.829928</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.326654</v>
+        <v>0.82839</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.111001</v>
+        <v>1.188925</v>
       </c>
     </row>
     <row r="37">
@@ -2657,34 +2653,34 @@
         </is>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.072604</v>
+        <v>0.001793</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.424249</v>
+        <v>0.21842</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.429818</v>
+        <v>0.33787</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.37961</v>
+        <v>0.317338</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.398025</v>
+        <v>0.038342</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>2.944359</v>
+        <v>0.051163</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>1.884972</v>
+        <v>0.759014</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>1.568323</v>
+        <v>0.063204</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.59931</v>
+        <v>0.09757399999999999</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>1.123008</v>
+        <v>0.045084</v>
       </c>
     </row>
     <row r="49">
@@ -7000,7 +6996,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -9878,7 +9874,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" s="5" t="n">
@@ -17216,7 +17212,7 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -21158,7 +21154,7 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">

--- a/output/pdf_financials_xlsx/TGOL.xlsx
+++ b/output/pdf_financials_xlsx/TGOL.xlsx
@@ -5878,10 +5878,10 @@
         </is>
       </c>
       <c r="D115" s="3" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="E115" s="3" t="n">
-        <v>0</v>
+        <v>0.0198</v>
       </c>
       <c r="F115" s="3" t="n">
         <v>0</v>
@@ -5902,10 +5902,10 @@
         <v>0</v>
       </c>
       <c r="L115" s="3" t="n">
-        <v>0</v>
+        <v>0.09575</v>
       </c>
       <c r="M115" s="3" t="n">
-        <v>0</v>
+        <v>0.301256</v>
       </c>
     </row>
     <row r="116">
@@ -12136,7 +12136,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -16060,7 +16064,11 @@
           <t>Proceeds from disposal of marketable securities</t>
         </is>
       </c>
-      <c r="D128" t="inlineStr"/>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E128" t="inlineStr">
         <is>
           <t>-</t>
